--- a/Config/Excel/DT_ProfessionWeaponPool.xlsx
+++ b/Config/Excel/DT_ProfessionWeaponPool.xlsx
@@ -5,12 +5,12 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\workspace\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\workspace\letsdeeprock-profession-preview\com-final-serial\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{4CCB136D-B821-451F-A143-721069DF2A6B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{002CC4C0-1D84-434A-B381-35B5E764C673}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="3900" yWindow="3900" windowWidth="28800" windowHeight="15345" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="38640" windowHeight="21120" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="66" uniqueCount="48">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="66" uniqueCount="50">
   <si>
     <t>#TABLE=DT_ProfessionWeaponPool</t>
   </si>
@@ -115,36 +115,6 @@
     <t>Ranger_ThrowingKnife</t>
   </si>
   <si>
-    <t>Driller_Primary_Flamethrower</t>
-  </si>
-  <si>
-    <t>爆破默认主武器</t>
-  </si>
-  <si>
-    <t>Driller</t>
-  </si>
-  <si>
-    <t>Driller_Flamethrower</t>
-  </si>
-  <si>
-    <t>Driller_Secondary_Revolver</t>
-  </si>
-  <si>
-    <t>爆破默认副武器</t>
-  </si>
-  <si>
-    <t>Driller_Revolver</t>
-  </si>
-  <si>
-    <t>Driller_Secondary_RocketLauncher</t>
-  </si>
-  <si>
-    <t>爆破副武器候选</t>
-  </si>
-  <si>
-    <t>Driller_RocketLauncher</t>
-  </si>
-  <si>
     <t>Engineer_Primary_AssaultRifle</t>
   </si>
   <si>
@@ -164,6 +134,54 @@
   </si>
   <si>
     <t>Engineer_ChainsawLauncher</t>
+  </si>
+  <si>
+    <t>Demolitionist_Primary_Flamethrower</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>Demolitionist default primary</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>Demolitionist</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>Primary</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>Demolitionist_Flamethrower</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>Demolitionist_Secondary_Revolver</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>Demolitionist default secondary</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>Secondary</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>Demolitionist_Revolver</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>Demolitionist_Secondary_RocketLauncher</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>Demolitionist secondary candidate</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>Demolitionist_RocketLauncher</t>
+    <phoneticPr fontId="1" type="noConversion"/>
   </si>
 </sst>
 </file>
@@ -666,19 +684,19 @@
     </row>
     <row r="9" spans="1:6" x14ac:dyDescent="0.15">
       <c r="A9" t="s">
-        <v>31</v>
+        <v>38</v>
       </c>
       <c r="B9" t="s">
-        <v>32</v>
+        <v>39</v>
       </c>
       <c r="C9" t="s">
-        <v>33</v>
+        <v>40</v>
       </c>
       <c r="D9" t="s">
-        <v>20</v>
+        <v>41</v>
       </c>
       <c r="E9" t="s">
-        <v>34</v>
+        <v>42</v>
       </c>
       <c r="F9">
         <v>1</v>
@@ -686,19 +704,19 @@
     </row>
     <row r="10" spans="1:6" x14ac:dyDescent="0.15">
       <c r="A10" t="s">
-        <v>35</v>
+        <v>43</v>
       </c>
       <c r="B10" t="s">
-        <v>36</v>
+        <v>44</v>
       </c>
       <c r="C10" t="s">
-        <v>33</v>
+        <v>40</v>
       </c>
       <c r="D10" t="s">
-        <v>24</v>
+        <v>45</v>
       </c>
       <c r="E10" t="s">
-        <v>37</v>
+        <v>46</v>
       </c>
       <c r="F10">
         <v>1</v>
@@ -706,19 +724,19 @@
     </row>
     <row r="11" spans="1:6" x14ac:dyDescent="0.15">
       <c r="A11" t="s">
-        <v>38</v>
+        <v>47</v>
       </c>
       <c r="B11" t="s">
-        <v>39</v>
+        <v>48</v>
       </c>
       <c r="C11" t="s">
-        <v>33</v>
+        <v>40</v>
       </c>
       <c r="D11" t="s">
-        <v>24</v>
+        <v>45</v>
       </c>
       <c r="E11" t="s">
-        <v>40</v>
+        <v>49</v>
       </c>
       <c r="F11">
         <v>0</v>
@@ -726,19 +744,19 @@
     </row>
     <row r="12" spans="1:6" x14ac:dyDescent="0.15">
       <c r="A12" t="s">
-        <v>41</v>
+        <v>31</v>
       </c>
       <c r="B12" t="s">
-        <v>42</v>
+        <v>32</v>
       </c>
       <c r="C12" t="s">
-        <v>43</v>
+        <v>33</v>
       </c>
       <c r="D12" t="s">
         <v>20</v>
       </c>
       <c r="E12" t="s">
-        <v>44</v>
+        <v>34</v>
       </c>
       <c r="F12">
         <v>1</v>
@@ -746,19 +764,19 @@
     </row>
     <row r="13" spans="1:6" x14ac:dyDescent="0.15">
       <c r="A13" t="s">
-        <v>45</v>
+        <v>35</v>
       </c>
       <c r="B13" t="s">
-        <v>46</v>
+        <v>36</v>
       </c>
       <c r="C13" t="s">
-        <v>43</v>
+        <v>33</v>
       </c>
       <c r="D13" t="s">
         <v>24</v>
       </c>
       <c r="E13" t="s">
-        <v>47</v>
+        <v>37</v>
       </c>
       <c r="F13">
         <v>1</v>
